--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>391483.6851034342</v>
+        <v>391484</v>
       </c>
       <c r="R2" t="n">
-        <v>6155015.043628554</v>
+        <v>6155015</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1997-05-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1997-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105713</v>
+        <v>105725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105725</v>
+        <v>105734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105734</v>
+        <v>105739</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105739</v>
+        <v>105767</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105767</v>
+        <v>105773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105773</v>
+        <v>105780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105780</v>
+        <v>105784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105784</v>
+        <v>105791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105794</v>
+        <v>105799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105799</v>
+        <v>105807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63432965</v>
       </c>
       <c r="B2" t="n">
-        <v>105807</v>
+        <v>105817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63432965</v>
+        <v>103252750</v>
       </c>
       <c r="B2" t="n">
-        <v>105817</v>
+        <v>90801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>655</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svartemosses norra del, Sk</t>
+          <t>Fortunaskogen, Fjällfotasjön, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>391484</v>
+        <v>391413</v>
       </c>
       <c r="R2" t="n">
-        <v>6155015</v>
+        <v>6155045</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-05-23</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-05-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Galium odoratum/2C1i3406/Hyby s:n/BSi/ /Bengt Sigfridson,Bara</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,88 +757,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>skogsvägkant</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    363535</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Mattis Christensen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Sigfridson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Mattis Christensen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103252750</v>
+        <v>133403060</v>
       </c>
       <c r="B3" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>655</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fortunaskogen, Fjällfotasjön, Sk</t>
+          <t>Fjällfotahus, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>391413.5153920294</v>
+        <v>392035</v>
       </c>
       <c r="R3" t="n">
-        <v>6155045.084722029</v>
+        <v>6154746</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +845,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,22 +869,137 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattis Ripsköld</t>
+          <t>Frida Fridh</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattis Ripsköld</t>
+          <t>Frida Fridh</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>63432965</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106328</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartemosses norra del, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>391484</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6155015</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1997-05-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1997-05-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Galium odoratum/2C1i3406/Hyby s:n/BSi/ /Bengt Sigfridson,Bara</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>skogsvägkant</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>SkFlora    363535</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bengt Sigfridson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16122-2024 artfynd.xlsx
+++ b/artfynd/A 16122-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103252750</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63432965</t>
         </is>
       </c>
     </row>
@@ -1000,8 +1015,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133403060</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>